--- a/sources/hwoarang_step5.xlsx
+++ b/sources/hwoarang_step5.xlsx
@@ -843,6 +843,11 @@
           <t>Can be done from LFF or RFF unless indicated otherwise</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>17408612-fc58-4f13-8e14-136748fa44ab</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>17408612-fc58-4f13-8e14-136748fa44ab</t>
@@ -895,6 +900,11 @@
           <t>In RFF 2+5 throws don't work.</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>b8fbde6d-1dd0-4a06-832a-6464328e437b</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>b8fbde6d-1dd0-4a06-832a-6464328e437b</t>
@@ -947,6 +957,11 @@
           <t>In RFF 2+5 throws don't work.</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>87427b97-ed62-47ff-9c16-7dd832dbaab9</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>87427b97-ed62-47ff-9c16-7dd832dbaab9</t>
@@ -997,6 +1012,11 @@
       <c r="O12" t="inlineStr">
         <is>
           <t>In RFF 2+5 throws don't work.</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>f5efc0a7-f776-4080-ad07-4baaea997c03</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -9856,6 +9876,11 @@
           <t>mhhLmmlhmh</t>
         </is>
       </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>43ddfb49-7ac4-4b7a-99bd-30c709526e89</t>
+        </is>
+      </c>
       <c r="Q182" t="inlineStr">
         <is>
           <t>43ddfb49-7ac4-4b7a-99bd-30c709526e89</t>
@@ -9886,6 +9911,11 @@
       <c r="K183" t="inlineStr">
         <is>
           <t>mhhLmmlhmh</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>b3e0a845-335b-4f9e-b80f-b2fcded6fdb7</t>
         </is>
       </c>
       <c r="Q183" t="inlineStr">
